--- a/employee_surveys/019_organizational_culture_assessment_form--employee_surveys.xlsx
+++ b/employee_surveys/019_organizational_culture_assessment_form--employee_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -520,12 +520,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>introduction</t>
+          <t>intro_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Welcome to our Organizational Culture Assessment Form</t>
+          <t>Introduction</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -548,7 +548,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>How do you communicate with your team and manager</t>
+          <t>How do you communicate with your team and manager?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -571,7 +571,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>What do you value most in our culture</t>
+          <t>What do you value most in our culture?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -594,7 +594,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>What do you like most about our workplace</t>
+          <t>What do you like most about our workplace?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -617,7 +617,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Is there anything we can improve on?</t>
+          <t>Do you get regular feedback from your manager and colleagues?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -635,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>communication_with_management</t>
+          <t>communication_with_manager</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>How often do you have face-to-face meetings with your manager?</t>
+          <t>Face-to-face meetings with your manager?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -663,7 +663,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>How often do you have team meetings</t>
+          <t>Team meetings?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -686,7 +686,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>How open-minded are your colleagues</t>
+          <t>How open-minded are your colleagues?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,7 +699,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>How much collaboration do you have with colleagues</t>
+          <t>How often do you collaborate with colleagues?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -745,17 +745,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>feedback_loops</t>
+          <t>feedback_from_colleagues</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>How often do you receive feedback from colleagues?</t>
+          <t>Do you get regular feedback from your colleagues?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -773,12 +773,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>organizational_culture</t>
+          <t>culture_value</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>How much do you value our organizational culture?</t>
+          <t>How much value do you place on our organizational culture?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -791,7 +791,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -819,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>work_life_balance</t>
+          <t>balance</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>How satisfied are you with your work-life balance?</t>
+          <t>Satisfaction with work-life balance?</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>employee_satisfaction</t>
+          <t>job_satisfaction</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>How satisfied are you with your job?</t>
+          <t>Job satisfaction?</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -860,17 +860,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>job_security</t>
+          <t>culture_value_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>How secure do you feel in your job?</t>
+          <t>Culture Value 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -883,17 +883,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>work_life_balance</t>
+          <t>intro_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>How satisfied are you with your work-life balance?</t>
+          <t>Intro 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -906,182 +906,21 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>communication_with_management</t>
+          <t>conclusion</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>How often do you have face-to-face meetings with your manager?</t>
+          <t>Conclusion</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>communication_with_colleagues</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>How often do you have team meetings?</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>open_mindedness</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>How open-minded are your colleagues?</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>collaboration</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>How much collaboration do you have with colleagues?</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>trust</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>How much do you trust your colleagues?</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>feedback_loops</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>How often do you receive feedback from colleagues?</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>organizational_culture</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>How much value do you put on our organizational culture?</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>organizational_culture</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>How much value do you put on our organizational culture?</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +937,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1194,51 +1033,51 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>communication_with_management_choices</t>
+          <t>communication_with_manager_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>frequent</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Frequent</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>communication_with_management_choices</t>
+          <t>communication_with_manager_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>occasional</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Occasional</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>communication_with_colleagues_choices</t>
+          <t>communication_with_manager_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -1250,46 +1089,233 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>frequent</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Frequent</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>feedback_loops_choices</t>
+          <t>communication_with_colleagues_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>occasional</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Occasional</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>feedback_loops_choices</t>
+          <t>communication_with_colleagues_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>Rarely</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>collaboration_choices</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>frequent</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Frequent</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>collaboration_choices</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>occasional</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Occasional</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>collaboration_choices</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>rarely</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Rarely</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>feedback_from_colleagues_choices</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>feedback_from_colleagues_choices</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
           <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>job_security_choices</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>frequent</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Frequent</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>job_security_choices</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>occasional</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Occasional</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>job_security_choices</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>rarely</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Rarely</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>culture_value_2_choices</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>frequent</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Frequent</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>culture_value_2_choices</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>occasional</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Occasional</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>culture_value_2_choices</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>rarely</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
